--- a/invoice_system_management/static/excel/invoice.xlsx
+++ b/invoice_system_management/static/excel/invoice.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,8 +439,9 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,10 +482,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>product_amount</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>product_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>invoice_total</t>
         </is>
@@ -493,20 +499,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45439</v>
+        <v>45455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>ishaan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>111111111111</t>
+          <t>82727293729</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>paid</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,13 +526,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1002.21</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1182.6078</v>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
